--- a/sheets/대금율보/검수/처녀 뱃사공.xlsx
+++ b/sheets/대금율보/검수/처녀 뱃사공.xlsx
@@ -3548,7 +3548,7 @@
       </c>
       <c r="H3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰‹
+          <t xml:space="preserve">汰
 仲</t>
         </is>
       </c>
@@ -3699,7 +3699,7 @@
       <c r="F6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">淋㳞
-淋㳞‹</t>
+淋㳞</t>
         </is>
       </c>
       <c r="G6" s="24" t="inlineStr">
@@ -3707,16 +3707,12 @@
           <t xml:space="preserve">버</t>
         </is>
       </c>
-      <c r="H6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H6" s="21"/>
       <c r="I6" s="24"/>
       <c r="J6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰潢
-無‹</t>
+無</t>
         </is>
       </c>
       <c r="K6" s="24"/>
@@ -3880,11 +3876,7 @@
       </c>
       <c r="D10" s="21"/>
       <c r="E10" s="24"/>
-      <c r="F10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="F10" s="21"/>
       <c r="G10" s="24"/>
       <c r="H10" s="21"/>
       <c r="I10" s="24"/>
@@ -4105,7 +4097,7 @@
       <c r="J14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰潢
-無‹</t>
+無</t>
         </is>
       </c>
       <c r="K14" s="24"/>

--- a/sheets/대금율보/검수/처녀 뱃사공.xlsx
+++ b/sheets/대금율보/검수/처녀 뱃사공.xlsx
@@ -3479,22 +3479,22 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="10.71" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="61.54" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -3511,7 +3511,7 @@
       <c r="J2" s="20"/>
       <c r="K2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="68.7" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -3565,7 +3565,7 @@
       </c>
       <c r="K3" s="22"/>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="68.7" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -3619,7 +3619,7 @@
       </c>
       <c r="K4" s="23"/>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="68.7" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -3672,7 +3672,7 @@
       </c>
       <c r="K5" s="23"/>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="68.7" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="K6" s="24"/>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="68.7" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -3770,7 +3770,7 @@
       </c>
       <c r="K7" s="22"/>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="68.7" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="K8" s="23"/>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="68.7" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -3862,7 +3862,7 @@
       <c r="J9" s="21"/>
       <c r="K9" s="23"/>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="68.7" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -3888,7 +3888,7 @@
       </c>
       <c r="K10" s="24"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="68.7" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -3942,7 +3942,7 @@
       </c>
       <c r="K11" s="22"/>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="68.7" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -3996,7 +3996,7 @@
       </c>
       <c r="K12" s="23"/>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="68.7" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="K13" s="23"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="68.7" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="K14" s="24"/>
     </row>
-    <row r="15" ht="56" customHeight="1">
+    <row r="15" ht="68.7" customHeight="true">
       <c r="A15" s="0"/>
       <c r="B15" s="21" t="inlineStr">
         <is>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="K15" s="22"/>
     </row>
-    <row r="16" ht="56" customHeight="1">
+    <row r="16" ht="68.7" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="21"/>
       <c r="C16" s="23"/>
@@ -4180,7 +4180,7 @@
       </c>
       <c r="K16" s="23"/>
     </row>
-    <row r="17" ht="56" customHeight="1">
+    <row r="17" ht="68.7" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="21" t="inlineStr">
         <is>
@@ -4221,7 +4221,7 @@
       </c>
       <c r="K17" s="23"/>
     </row>
-    <row r="18" ht="56" customHeight="1">
+    <row r="18" ht="68.7" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="21" t="inlineStr">
         <is>
@@ -4268,6 +4268,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="77"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="65"/>
 </worksheet>
 </file>